--- a/data/trans_camb/P2A_fisi_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 7,53</t>
+          <t>-2,46; 6,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 9,85</t>
+          <t>-1,08; 9,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,12</t>
+          <t>-4,03; 2,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 16,44</t>
+          <t>-1,59; 15,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 10,69</t>
+          <t>-2,16; 10,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 8,03</t>
+          <t>-3,93; 8,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 10,84</t>
+          <t>-0,83; 9,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 8,09</t>
+          <t>-0,24; 7,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,27</t>
+          <t>-2,47; 4,23</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,63; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,24 +813,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-69,5; 1505,16</t>
+          <t>-64,89; 1334,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,26; —</t>
+          <t>-45,54; 1232,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-73,58; —</t>
+          <t>-85,04; 831,05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 1,71</t>
+          <t>-5,75; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 6,1</t>
+          <t>-3,65; 7,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 8,67</t>
+          <t>-1,76; 9,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 8,6</t>
+          <t>-3,79; 7,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,67</t>
+          <t>-8,41; 1,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 7,6</t>
+          <t>-3,97; 7,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,97</t>
+          <t>-3,19; 3,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,23</t>
+          <t>-4,17; 2,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 6,62</t>
+          <t>-1,58; 6,38</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,74; 826,77</t>
+          <t>-48,88; 1005,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,41; 536,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,29 +1024,29 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,2; 557,07</t>
+          <t>-67,39; 445,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,25; 302,7</t>
+          <t>-74,38; 241,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,62; 186,39</t>
+          <t>-86,07; 195,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 390,53</t>
+          <t>-36,19; 377,47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,24</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,28</t>
+          <t>0,88; 9,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,47</t>
+          <t>-2,77; 6,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,0</t>
+          <t>-6,48; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 13,84</t>
+          <t>2,17; 14,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,24</t>
+          <t>-1,2; 4,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,0</t>
+          <t>-3,76; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 9,76</t>
+          <t>3,12; 10,74</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,44; —</t>
+          <t>0,12; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,67; —</t>
+          <t>77,98; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 2,57</t>
+          <t>-3,99; 3,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 11,27</t>
+          <t>-0,97; 11,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 1,56</t>
+          <t>-5,25; 1,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 7,96</t>
+          <t>-1,61; 8,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 4,9</t>
+          <t>-3,23; 4,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 11,26</t>
+          <t>-0,93; 11,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,71</t>
+          <t>-1,5; 4,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 6,2</t>
+          <t>-1,28; 5,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 5,93</t>
+          <t>-1,35; 6,21</t>
         </is>
       </c>
     </row>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1104,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1505,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,2; 1433,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 14,95</t>
+          <t>-21,39; 14,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 0,0</t>
+          <t>-32,68; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 6,46</t>
+          <t>-27,61; 6,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,08</t>
+          <t>0,0; 13,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,09</t>
+          <t>0,0; 12,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,9</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 7,6</t>
+          <t>-9,75; 7,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 2,76</t>
+          <t>-13,65; 2,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 4,17</t>
+          <t>-11,94; 4,27</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,66; 15,02</t>
+          <t>1,69; 13,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,92</t>
+          <t>0,0; 15,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,68; 17,3</t>
+          <t>4,26; 17,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,68</t>
+          <t>-5,72; 5,74</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 5,66</t>
+          <t>-5,4; 7,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,29; 20,28</t>
+          <t>2,92; 18,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 7,35</t>
+          <t>-0,57; 7,04</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 7,89</t>
+          <t>-1,47; 7,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,84; 16,25</t>
+          <t>5,41; 15,78</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,51; —</t>
+          <t>-19,8; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>107,73; —</t>
+          <t>97,23; —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,72</t>
+          <t>-2,44; 6,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,74</t>
+          <t>-3,22; 3,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,39; 12,51</t>
+          <t>2,11; 11,94</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 1,67</t>
+          <t>-5,9; 1,65</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 4,25</t>
+          <t>-4,65; 3,98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 11,67</t>
+          <t>-2,25; 10,99</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,48</t>
+          <t>-2,74; 2,73</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,64</t>
+          <t>-3,01; 2,71</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,8</t>
+          <t>1,59; 10,11</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-65,72; 550,74</t>
+          <t>-69,34; 730,08</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-85,34; 529,8</t>
+          <t>-86,69; 582,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36,68; 1449,64</t>
+          <t>20,38; 1519,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-88,84; 194,61</t>
+          <t>-90,87; 192,32</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-77,11; 335,94</t>
+          <t>-81,66; 277,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 670,43</t>
+          <t>-54,12; 589,51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-62,63; 135,62</t>
+          <t>-63,2; 154,86</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-66,46; 139,43</t>
+          <t>-67,44; 153,44</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18,52; 493,88</t>
+          <t>18,04; 486,97</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,28</t>
+          <t>-4,79; 1,96</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,61</t>
+          <t>-4,0; 3,22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,54</t>
+          <t>-2,65; 4,98</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 2,07</t>
+          <t>-7,46; 1,84</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,39; -1,9</t>
+          <t>-9,95; -1,89</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 1,94</t>
+          <t>-7,76; 1,87</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 1,02</t>
+          <t>-4,84; 1,1</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,22</t>
+          <t>-6,26; -0,33</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 2,24</t>
+          <t>-4,5; 2,22</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-82,62; —</t>
+          <t>-88,5; 470,1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,71; 736,32</t>
+          <t>-72,72; 691,81</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-82,42; 73,64</t>
+          <t>-81,33; 55,76</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -39,74</t>
+          <t>-100,0; -16,35</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-79,63; 72,01</t>
+          <t>-82,04; 66,51</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-76,32; 49,72</t>
+          <t>-75,74; 51,43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-85,92; 5,88</t>
+          <t>-87,62; 10,97</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-61,41; 92,27</t>
+          <t>-64,93; 83,96</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,63</t>
+          <t>-0,48; 2,69</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,38</t>
+          <t>-0,54; 2,43</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,31</t>
+          <t>1,63; 5,06</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,01</t>
+          <t>-1,6; 2,02</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,43</t>
+          <t>-2,81; 0,42</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,89</t>
+          <t>0,5; 4,98</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,79</t>
+          <t>-0,67; 1,69</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,91</t>
+          <t>-1,29; 0,97</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,44</t>
+          <t>1,62; 4,55</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 226,97</t>
+          <t>-23,61; 226,94</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 213,54</t>
+          <t>-22,92; 227,7</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>61,9; 479,42</t>
+          <t>57,82; 471,35</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 83,57</t>
+          <t>-38,18; 78,49</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-64,85; 20,28</t>
+          <t>-65,35; 21,11</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9,16; 184,63</t>
+          <t>8,32; 192,01</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 85,41</t>
+          <t>-21,31; 86,76</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-40,84; 44,8</t>
+          <t>-41,62; 48,6</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>48,08; 211,19</t>
+          <t>46,81; 224,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 6,8</t>
+          <t>-2,44; 6,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 9,4</t>
+          <t>-1,2; 9,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,15</t>
+          <t>-4,88; 1,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 15,1</t>
+          <t>-2,74; 13,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 10,26</t>
+          <t>-2,9; 10,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 8,08</t>
+          <t>-3,29; 8,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 9,81</t>
+          <t>-1,43; 9,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 7,93</t>
+          <t>-0,65; 8,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,23</t>
+          <t>-2,33; 4,26</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-90,63; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,67; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,89; 1334,3</t>
+          <t>-72,94; 1306,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 1232,5</t>
+          <t>-51,21; 1136,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,04; 831,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 1,74</t>
+          <t>-5,51; 2,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 7,01</t>
+          <t>-3,72; 6,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 9,0</t>
+          <t>-2,81; 8,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 7,78</t>
+          <t>-3,63; 8,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 1,37</t>
+          <t>-7,24; 1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 7,16</t>
+          <t>-4,16; 7,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,6</t>
+          <t>-3,24; 3,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,48</t>
+          <t>-4,01; 2,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 6,38</t>
+          <t>-1,42; 6,23</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 1005,07</t>
+          <t>-54,88; 828,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,41; 536,88</t>
+          <t>-73,17; 659,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,39; 445,68</t>
+          <t>-68,7; 657,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,38; 241,58</t>
+          <t>-68,1; 247,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,07; 195,16</t>
+          <t>-87,99; 181,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 377,47</t>
+          <t>-32,88; 343,07</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 10,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,13</t>
+          <t>1,07; 9,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,17</t>
+          <t>-3,0; 5,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 0,0</t>
+          <t>-6,45; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 14,69</t>
+          <t>2,01; 15,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 4,74</t>
+          <t>-1,22; 4,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,0</t>
+          <t>-3,32; 0,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 10,74</t>
+          <t>2,76; 10,24</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,12; —</t>
+          <t>-5,1; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77,98; —</t>
+          <t>33,86; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,59</t>
+          <t>-4,04; 2,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 11,6</t>
+          <t>-1,23; 11,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 1,44</t>
+          <t>-5,28; 1,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 8,23</t>
+          <t>-1,63; 8,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,78</t>
+          <t>-3,27; 4,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 11,61</t>
+          <t>-1,26; 12,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,56</t>
+          <t>-1,72; 4,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,83</t>
+          <t>-1,55; 6,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,21</t>
+          <t>-1,4; 5,36</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-87,2; 1433,2</t>
+          <t>-88,47; 1229,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 14,81</t>
+          <t>-21,06; 14,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 0,0</t>
+          <t>-33,75; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-27,61; 6,24</t>
+          <t>-23,92; 6,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,28</t>
+          <t>0,0; 10,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,93</t>
+          <t>0,0; 10,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,89</t>
+          <t>0,0; 9,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 7,73</t>
+          <t>-10,04; 6,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 2,76</t>
+          <t>-11,9; 2,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 4,27</t>
+          <t>-11,69; 4,42</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,69; 13,92</t>
+          <t>1,64; 14,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,15</t>
+          <t>0,0; 15,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,26; 17,59</t>
+          <t>4,51; 17,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 5,74</t>
+          <t>-4,31; 5,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 7,31</t>
+          <t>-5,4; 5,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,92; 18,59</t>
+          <t>3,83; 20,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 7,04</t>
+          <t>-0,45; 7,39</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 7,24</t>
+          <t>-1,58; 8,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,41; 15,78</t>
+          <t>5,08; 16,31</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-19,8; —</t>
+          <t>18,49; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-60,23; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>97,23; —</t>
+          <t>81,65; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 6,06</t>
+          <t>-2,02; 6,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 3,65</t>
+          <t>-3,12; 4,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,11; 11,94</t>
+          <t>2,13; 12,59</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 1,65</t>
+          <t>-5,56; 1,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,98</t>
+          <t>-4,38; 4,34</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,99</t>
+          <t>-1,5; 12,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,73</t>
+          <t>-2,52; 2,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,71</t>
+          <t>-2,78; 2,79</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,59; 10,11</t>
+          <t>1,16; 9,78</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-69,34; 730,08</t>
+          <t>-56,04; 893,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-86,69; 582,79</t>
+          <t>-83,59; 727,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20,38; 1519,45</t>
+          <t>29,22; 1422,51</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-90,87; 192,32</t>
+          <t>-90,75; 137,13</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-81,66; 277,95</t>
+          <t>-76,65; 292,06</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 589,51</t>
+          <t>-49,4; 614,27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-63,2; 154,86</t>
+          <t>-61,23; 146,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-67,44; 153,44</t>
+          <t>-63,97; 163,47</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18,04; 486,97</t>
+          <t>12,83; 484,06</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,96</t>
+          <t>-5,03; 2,19</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,22</t>
+          <t>-3,77; 3,18</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 4,98</t>
+          <t>-2,31; 5,39</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,84</t>
+          <t>-8,13; 1,82</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,95; -1,89</t>
+          <t>-11,0; -1,93</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 1,87</t>
+          <t>-8,78; 1,7</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,1</t>
+          <t>-4,83; 0,98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,26; -0,33</t>
+          <t>-6,1; -0,31</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,22</t>
+          <t>-4,47; 2,18</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-88,5; 470,1</t>
+          <t>-81,65; inf</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-72,72; 691,81</t>
+          <t>-65,37; 847,14</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-81,33; 55,76</t>
+          <t>-80,48; 75,61</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-82,04; 66,51</t>
+          <t>-83,31; 68,21</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 51,43</t>
+          <t>-76,25; 43,15</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-87,62; 10,97</t>
+          <t>-87,23; 10,63</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-64,93; 83,96</t>
+          <t>-64,65; 87,25</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,69</t>
+          <t>-0,43; 2,71</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,43</t>
+          <t>-0,57; 2,42</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,06</t>
+          <t>1,78; 5,12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,02</t>
+          <t>-1,73; 2,01</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,42</t>
+          <t>-2,96; 0,56</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,98</t>
+          <t>0,62; 5,04</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,69</t>
+          <t>-0,58; 1,83</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,97</t>
+          <t>-1,33; 0,95</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,55</t>
+          <t>1,68; 4,47</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 226,94</t>
+          <t>-21,71; 250,46</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 227,7</t>
+          <t>-27,8; 207,92</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>57,82; 471,35</t>
+          <t>60,79; 451,16</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 78,49</t>
+          <t>-41,21; 81,66</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-65,35; 21,11</t>
+          <t>-67,88; 22,89</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>8,32; 192,01</t>
+          <t>12,54; 202,87</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 86,76</t>
+          <t>-18,64; 97,96</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 48,6</t>
+          <t>-41,2; 46,21</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>46,81; 224,96</t>
+          <t>51,97; 211,4</t>
         </is>
       </c>
     </row>
